--- a/presets-source/LSA/Lesson 7/Lesson 7 - Vocab 3.xlsx
+++ b/presets-source/LSA/Lesson 7/Lesson 7 - Vocab 3.xlsx
@@ -5,11 +5,11 @@
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ksh12\Projects\vocab-study\presets-source\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ksh12\Projects\vocab-study\presets-source\LSA\Lesson 7\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="22788" windowHeight="8256" tabRatio="500"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="11100" windowHeight="8232" tabRatio="500"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="시트1" sheetId="1" r:id="rId4"/>
@@ -19,25 +19,145 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+  <x:si>
+    <x:t>He thought he might be zapped into a black hole or bump into a satellite.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>중얼거리다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>v. to move quickly or suddenly</x:t>
+  </x:si>
+  <x:si>
+    <x:t>n. a section of a town or city</x:t>
+  </x:si>
+  <x:si>
+    <x:t>n. any point in the air</x:t>
+  </x:si>
+  <x:si>
+    <x:t>n. the hair that grows on a man's cheeks and chin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>croak - croaked</x:t>
+  </x:si>
+  <x:si>
+    <x:t>surround - surrounded</x:t>
+  </x:si>
+  <x:si>
+    <x:t>midair</x:t>
+  </x:si>
+  <x:si>
+    <x:t>beard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>storm</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mumble - mumbled</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공중</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영어 문장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한글 뜻</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영어 단어</x:t>
+  </x:si>
   <x:si>
     <x:t>영어 뜻</x:t>
   </x:si>
   <x:si>
-    <x:t>영어 문장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영어 단어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한글 뜻</x:t>
+    <x:t>동네, 이웃</x:t>
+  </x:si>
+  <x:si>
+    <x:t>He was surrounded by white clouds.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Jimmy was flying in midair.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>adj. confused</x:t>
+  </x:si>
+  <x:si>
+    <x:t>neighborhood</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"I... I don't know," mumbled Jimmy.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>He lost sight of the streets and the trees and the whole neighborhood.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>exclaim - exclaimed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"Hey! What are you doing here, young man?" asked one of the men with a long beard.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>재빨리 움직이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어리둥절해 하는</x:t>
+  </x:si>
+  <x:si>
+    <x:t>n. bad weather in which there is a lot of rain, snow, etc.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소리치다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>puzzled</x:t>
+  </x:si>
+  <x:si>
+    <x:t>v. to say something in a rough, low voice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zap - zapped</x:t>
+  </x:si>
+  <x:si>
+    <x:t>폭풍</x:t>
+  </x:si>
+  <x:si>
+    <x:t>둘러싸다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(턱) 수염</x:t>
+  </x:si>
+  <x:si>
+    <x:t>v. to be on every side of someone or something</x:t>
+  </x:si>
+  <x:si>
+    <x:t>v. to say something in a quiet, unclear voice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"I can hear the storm in your head," the bearded man said.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>He passed by puzzled birds as he flew up toward the clouds.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(목이 쉰 듯) 말하다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"W... What?" Jimmy croaked.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>v. to cry out suddenly</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"Boy, isn't that noisy!" exclaimed the other man.</x:t>
   </x:si>
 </x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="6">
+  <x:fonts count="7">
     <x:font>
       <x:name val="Arial"/>
       <x:sz val="10"/>
@@ -66,6 +186,11 @@
     <x:font>
       <x:name val="Arial"/>
       <x:sz val="10"/>
+      <x:color rgb="ff000000"/>
+    </x:font>
+    <x:font>
+      <x:name val="맑은 고딕"/>
+      <x:sz val="11"/>
       <x:color rgb="ff000000"/>
     </x:font>
   </x:fonts>
@@ -711,113 +836,196 @@
   <x:sheetPr codeName="Sheet1"/>
   <x:dimension ref="A1:E11"/>
   <x:sheetFormatPr defaultColWidth="12.62890625" defaultRowHeight="15.75" customHeight="1"/>
+  <x:cols>
+    <x:col min="4" max="4" width="17.33203125" customWidth="1"/>
+  </x:cols>
   <x:sheetData>
     <x:row r="1" spans="2:5" ht="13.199999999999999">
       <x:c r="B1" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:5" ht="13.199999999999999">
       <x:c r="A2" s="1">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B2" s="1"/>
-      <x:c r="C2" s="1"/>
-      <x:c r="D2" s="1"/>
-      <x:c r="E2" s="1"/>
+      <x:c r="B2" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D2" s="1" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E2" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" spans="1:5" ht="13.199999999999999">
       <x:c r="A3" s="1">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B3" s="1"/>
-      <x:c r="C3" s="1"/>
-      <x:c r="D3" s="1"/>
-      <x:c r="E3" s="1"/>
+      <x:c r="B3" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C3" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D3" s="1" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E3" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" spans="1:5" ht="13.199999999999999">
       <x:c r="A4" s="1">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B4" s="1"/>
-      <x:c r="C4" s="1"/>
-      <x:c r="D4" s="1"/>
-      <x:c r="E4" s="1"/>
+      <x:c r="B4" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C4" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D4" s="1" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E4" s="1" t="s">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" spans="1:5" ht="13.199999999999999">
       <x:c r="A5" s="1">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B5" s="1"/>
-      <x:c r="C5" s="1"/>
-      <x:c r="D5" s="1"/>
-      <x:c r="E5" s="1"/>
+      <x:c r="B5" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C5" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D5" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E5" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" spans="1:5" ht="13.199999999999999">
       <x:c r="A6" s="1">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B6" s="1"/>
-      <x:c r="C6" s="1"/>
-      <x:c r="D6" s="1"/>
-      <x:c r="E6" s="1"/>
+      <x:c r="B6" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C6" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D6" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E6" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" spans="1:5" ht="13.199999999999999">
       <x:c r="A7" s="1">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B7" s="1"/>
-      <x:c r="C7" s="1"/>
-      <x:c r="D7" s="1"/>
-      <x:c r="E7" s="1"/>
+      <x:c r="B7" s="1" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C7" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D7" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E7" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" spans="1:5" ht="13.199999999999999">
       <x:c r="A8" s="1">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B8" s="1"/>
-      <x:c r="C8" s="1"/>
-      <x:c r="D8" s="1"/>
-      <x:c r="E8" s="1"/>
+      <x:c r="B8" s="1" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C8" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D8" s="1" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E8" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" spans="1:5" ht="13.199999999999999">
       <x:c r="A9" s="1">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B9" s="1"/>
-      <x:c r="C9" s="1"/>
-      <x:c r="D9" s="1"/>
-      <x:c r="E9" s="1"/>
+      <x:c r="B9" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C9" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D9" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E9" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" spans="1:5" ht="13.199999999999999">
       <x:c r="A10" s="1">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B10" s="1"/>
-      <x:c r="C10" s="1"/>
-      <x:c r="D10" s="1"/>
-      <x:c r="E10" s="1"/>
+      <x:c r="B10" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C10" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D10" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E10" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" spans="1:5" ht="13.199999999999999">
       <x:c r="A11" s="1">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B11" s="1"/>
-      <x:c r="C11" s="1"/>
-      <x:c r="D11" s="1"/>
-      <x:c r="E11" s="1"/>
+      <x:c r="B11" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C11" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D11" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E11" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.74805557727813721" right="0.74805557727813721" top="0.98430556058883667" bottom="0.98430556058883667" header="0.51180553436279297" footer="0.51180553436279297"/>
+  <x:pageMargins left="0.74805557727813721" right="0.74805557727813721" top="0.98430556058883667" bottom="0.98430556058883667" header="0.51166665554046631" footer="0.51166665554046631"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>